--- a/public/sample_import_data/job_functions.xlsx
+++ b/public/sample_import_data/job_functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\visibleone\projects\example-app\public\sample_import_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3858C5A-A21E-4F74-9212-1EC28848E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0739DA4-3DFC-4CA3-A0B2-F345DF513CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Name</t>
   </si>
@@ -32,6 +32,12 @@
   </si>
   <si>
     <t>Software Development and Management</t>
+  </si>
+  <si>
+    <t>Is Active</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -371,30 +377,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{BF021B77-15F2-4108-AF38-AE559077E6F1}">
+      <formula1>"Yes, No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>